--- a/SRPT.xlsx
+++ b/SRPT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804A093F-01AE-4769-A2FF-BDC3218E2410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0E47C0-AF8B-4A02-B0EC-7232E60B4DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17460" yWindow="6790" windowWidth="19170" windowHeight="13220" activeTab="1" xr2:uid="{79CAE26F-8736-4C5E-9FC6-A2D7A01B0567}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="22360" windowHeight="16580" xr2:uid="{79CAE26F-8736-4C5E-9FC6-A2D7A01B0567}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -46,11 +46,16 @@
     <author>tc={E6AB6E99-1C3B-4950-9986-65466B8F87A6}</author>
     <author>tc={04498D6E-3C18-4A5B-A908-2E60D972CB97}</author>
     <author>tc={24D42E51-CC70-433B-B635-28ADB495B3B2}</author>
+    <author>tc={F38E3BCE-C099-46AC-85CD-4F0263F82F5D}</author>
+    <author>tc={1468DC2E-37B2-4A9D-8B73-E1A21385BB94}</author>
     <author>tc={6230A4A9-C9AF-4BE7-99BF-B573BD017A22}</author>
     <author>tc={CBA3C9AE-8CDE-4C14-99CA-A98DB0CE1BE6}</author>
     <author>tc={5AFD68C2-EA74-46FE-BF40-AB537FB76AE8}</author>
     <author>tc={7C3EC1BA-FB3C-4FE0-8E5F-1192557AF098}</author>
     <author>tc={4F81179F-16E6-41BC-B914-AFAB95CADEE2}</author>
+    <author>tc={441CB689-8F02-4EDC-B0C9-7BC5B621D715}</author>
+    <author>tc={B69FD0CC-3C54-4933-9C26-7CC64144E00B}</author>
+    <author>tc={F6286F19-9218-4997-BA32-30CAB450B42C}</author>
     <author>tc={79BDC40B-94ED-4D00-94B2-1CB4305DAAA9}</author>
     <author>tc={4BF41E21-6626-4EBB-BC28-DD3A3AEE92C2}</author>
     <author>tc={9D7C51D0-BE73-45DC-971C-65116E6017D9}</author>
@@ -80,7 +85,23 @@
     $226m consensus</t>
       </text>
     </comment>
-    <comment ref="W13" authorId="3" shapeId="0" xr:uid="{6230A4A9-C9AF-4BE7-99BF-B573BD017A22}">
+    <comment ref="AV11" authorId="3" shapeId="0" xr:uid="{F38E3BCE-C099-46AC-85CD-4F0263F82F5D}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Q126: reiterated 1.2-1.4B</t>
+      </text>
+    </comment>
+    <comment ref="AA12" authorId="4" shapeId="0" xr:uid="{1468DC2E-37B2-4A9D-8B73-E1A21385BB94}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Chugai 40m milestone for Japan first sale</t>
+      </text>
+    </comment>
+    <comment ref="W13" authorId="5" shapeId="0" xr:uid="{6230A4A9-C9AF-4BE7-99BF-B573BD017A22}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -88,7 +109,7 @@
     5/6/25 consensus 687m </t>
       </text>
     </comment>
-    <comment ref="X13" authorId="4" shapeId="0" xr:uid="{CBA3C9AE-8CDE-4C14-99CA-A98DB0CE1BE6}">
+    <comment ref="X13" authorId="6" shapeId="0" xr:uid="{CBA3C9AE-8CDE-4C14-99CA-A98DB0CE1BE6}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -96,7 +117,7 @@
     5/6/25 consensus 741m</t>
       </text>
     </comment>
-    <comment ref="Y13" authorId="5" shapeId="0" xr:uid="{5AFD68C2-EA74-46FE-BF40-AB537FB76AE8}">
+    <comment ref="Y13" authorId="7" shapeId="0" xr:uid="{5AFD68C2-EA74-46FE-BF40-AB537FB76AE8}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -105,7 +126,7 @@
 11/3/25 consensus: 336m</t>
       </text>
     </comment>
-    <comment ref="Z13" authorId="6" shapeId="0" xr:uid="{7C3EC1BA-FB3C-4FE0-8E5F-1192557AF098}">
+    <comment ref="Z13" authorId="8" shapeId="0" xr:uid="{7C3EC1BA-FB3C-4FE0-8E5F-1192557AF098}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -114,7 +135,7 @@
 11/3/25 consensus: 351m</t>
       </text>
     </comment>
-    <comment ref="AA13" authorId="7" shapeId="0" xr:uid="{4F81179F-16E6-41BC-B914-AFAB95CADEE2}">
+    <comment ref="AA13" authorId="9" shapeId="0" xr:uid="{4F81179F-16E6-41BC-B914-AFAB95CADEE2}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -122,7 +143,31 @@
     474m consensus 5/4/26</t>
       </text>
     </comment>
-    <comment ref="AU13" authorId="8" shapeId="0" xr:uid="{79BDC40B-94ED-4D00-94B2-1CB4305DAAA9}">
+    <comment ref="AB13" authorId="10" shapeId="0" xr:uid="{441CB689-8F02-4EDC-B0C9-7BC5B621D715}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    7/6/26: 365m consensus</t>
+      </text>
+    </comment>
+    <comment ref="AC13" authorId="11" shapeId="0" xr:uid="{B69FD0CC-3C54-4933-9C26-7CC64144E00B}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    7/6/26: 372m consensus</t>
+      </text>
+    </comment>
+    <comment ref="AD13" authorId="12" shapeId="0" xr:uid="{F6286F19-9218-4997-BA32-30CAB450B42C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    7/6/26: 377m consensus</t>
+      </text>
+    </comment>
+    <comment ref="AU13" authorId="13" shapeId="0" xr:uid="{79BDC40B-94ED-4D00-94B2-1CB4305DAAA9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -131,7 +176,7 @@
 Consensus 3.0B</t>
       </text>
     </comment>
-    <comment ref="AV13" authorId="9" shapeId="0" xr:uid="{4BF41E21-6626-4EBB-BC28-DD3A3AEE92C2}">
+    <comment ref="AV13" authorId="14" shapeId="0" xr:uid="{4BF41E21-6626-4EBB-BC28-DD3A3AEE92C2}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -140,7 +185,7 @@
 3/20/26 consensus 1.71B</t>
       </text>
     </comment>
-    <comment ref="AW13" authorId="10" shapeId="0" xr:uid="{9D7C51D0-BE73-45DC-971C-65116E6017D9}">
+    <comment ref="AW13" authorId="15" shapeId="0" xr:uid="{9D7C51D0-BE73-45DC-971C-65116E6017D9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -153,7 +198,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="260">
   <si>
     <t>Price</t>
   </si>
@@ -815,9 +860,6 @@
     <t>IND 1H25</t>
   </si>
   <si>
-    <t>I/II - 2H25 results</t>
-  </si>
-  <si>
     <t>HTT</t>
   </si>
   <si>
@@ -930,6 +972,12 @@
   </si>
   <si>
     <t>SRP-1005 (ARO-HTT)</t>
+  </si>
+  <si>
+    <t>Share</t>
+  </si>
+  <si>
+    <t>Terminal</t>
   </si>
 </sst>
 </file>
@@ -1187,16 +1235,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>25121</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>49544</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>8512</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>25121</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>49544</xdr:colOff>
       <xdr:row>82</xdr:row>
-      <xdr:rowOff>39077</xdr:rowOff>
+      <xdr:rowOff>30565</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1211,7 +1259,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16740275" y="8512"/>
+          <a:off x="17375275" y="0"/>
           <a:ext cx="0" cy="13253219"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1238,15 +1286,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>46</xdr:col>
-      <xdr:colOff>26737</xdr:colOff>
+      <xdr:colOff>593352</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>50132</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>46</xdr:col>
-      <xdr:colOff>26737</xdr:colOff>
+      <xdr:colOff>593352</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>122115</xdr:rowOff>
+      <xdr:rowOff>71983</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1261,8 +1309,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="26559968" y="50132"/>
-          <a:ext cx="0" cy="10070791"/>
+          <a:off x="29568890" y="0"/>
+          <a:ext cx="0" cy="10231983"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1825,6 +1873,12 @@
   <threadedComment ref="AA7" dT="2026-05-04T14:36:22.45" personId="{0ED4F94C-7603-49B0-A19F-451A0F5F06CB}" id="{24D42E51-CC70-433B-B635-28ADB495B3B2}">
     <text>$226m consensus</text>
   </threadedComment>
+  <threadedComment ref="AV11" dT="2026-07-06T17:55:46.72" personId="{0ED4F94C-7603-49B0-A19F-451A0F5F06CB}" id="{F38E3BCE-C099-46AC-85CD-4F0263F82F5D}">
+    <text>Q126: reiterated 1.2-1.4B</text>
+  </threadedComment>
+  <threadedComment ref="AA12" dT="2026-07-06T18:03:04.42" personId="{0ED4F94C-7603-49B0-A19F-451A0F5F06CB}" id="{1468DC2E-37B2-4A9D-8B73-E1A21385BB94}">
+    <text>Chugai 40m milestone for Japan first sale</text>
+  </threadedComment>
   <threadedComment ref="W13" dT="2025-05-06T15:45:31.88" personId="{0ED4F94C-7603-49B0-A19F-451A0F5F06CB}" id="{6230A4A9-C9AF-4BE7-99BF-B573BD017A22}">
     <text xml:space="preserve">5/6/25 consensus 687m </text>
   </threadedComment>
@@ -1841,6 +1895,15 @@
   </threadedComment>
   <threadedComment ref="AA13" dT="2026-05-04T14:14:19.13" personId="{0ED4F94C-7603-49B0-A19F-451A0F5F06CB}" id="{4F81179F-16E6-41BC-B914-AFAB95CADEE2}">
     <text>474m consensus 5/4/26</text>
+  </threadedComment>
+  <threadedComment ref="AB13" dT="2026-07-06T18:29:10.04" personId="{0ED4F94C-7603-49B0-A19F-451A0F5F06CB}" id="{441CB689-8F02-4EDC-B0C9-7BC5B621D715}">
+    <text>7/6/26: 365m consensus</text>
+  </threadedComment>
+  <threadedComment ref="AC13" dT="2026-07-06T18:29:21.77" personId="{0ED4F94C-7603-49B0-A19F-451A0F5F06CB}" id="{B69FD0CC-3C54-4933-9C26-7CC64144E00B}">
+    <text>7/6/26: 372m consensus</text>
+  </threadedComment>
+  <threadedComment ref="AD13" dT="2026-07-06T18:29:38.65" personId="{0ED4F94C-7603-49B0-A19F-451A0F5F06CB}" id="{F6286F19-9218-4997-BA32-30CAB450B42C}">
+    <text>7/6/26: 377m consensus</text>
   </threadedComment>
   <threadedComment ref="AU13" dT="2025-05-06T15:53:17.18" personId="{0ED4F94C-7603-49B0-A19F-451A0F5F06CB}" id="{79BDC40B-94ED-4D00-94B2-1CB4305DAAA9}">
     <text>Q424 product guidance: 2.9-3.1B
@@ -1889,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>21</v>
+        <v>19.48</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
@@ -1904,11 +1967,10 @@
         <v>1</v>
       </c>
       <c r="L3" s="2">
-        <f>105.615096-0.650876</f>
-        <v>104.96422</v>
+        <v>105.576222</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>63</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
@@ -1933,7 +1995,7 @@
       </c>
       <c r="L4" s="2">
         <f>+L2*L3</f>
-        <v>2204.2486199999998</v>
+        <v>2056.62480456</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
@@ -1948,11 +2010,11 @@
         <v>3</v>
       </c>
       <c r="L5" s="2">
-        <f>801.282+138.368</f>
-        <v>939.65000000000009</v>
+        <f>464.45+188.739+81.936</f>
+        <v>735.125</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>63</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
@@ -1967,10 +2029,10 @@
         <v>4</v>
       </c>
       <c r="L6" s="2">
-        <v>828.97400000000005</v>
+        <v>838.16200000000003</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>63</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
@@ -1989,7 +2051,7 @@
       </c>
       <c r="L7" s="2">
         <f>+L4-L5+L6</f>
-        <v>2093.5726199999999</v>
+        <v>2159.6618045599998</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
@@ -2062,7 +2124,7 @@
         <v>209</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="E11" t="s">
         <v>210</v>
@@ -2080,7 +2142,7 @@
         <v>213</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="E12" t="s">
         <v>211</v>
@@ -2090,7 +2152,7 @@
       </c>
       <c r="I12" s="10"/>
       <c r="K12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L12" s="2">
         <v>345.125</v>
@@ -2176,7 +2238,7 @@
         <v>172</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E17" t="s">
         <v>200</v>
@@ -2200,16 +2262,16 @@
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C19" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D19" s="29" t="s">
         <v>170</v>
       </c>
       <c r="E19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F19" t="s">
         <v>111</v>
@@ -2218,16 +2280,16 @@
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C20" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D20" s="29" t="s">
         <v>169</v>
       </c>
       <c r="E20" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F20" t="s">
         <v>111</v>
@@ -2236,16 +2298,16 @@
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C21" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D21" s="29" t="s">
         <v>169</v>
       </c>
       <c r="E21" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F21" t="s">
         <v>111</v>
@@ -2291,7 +2353,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3CE2201-9B97-4447-A1A2-DF8707285205}">
-  <dimension ref="A1:BH75"/>
+  <dimension ref="A1:BW75"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -2381,16 +2443,16 @@
         <v>63</v>
       </c>
       <c r="AA2" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB2" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="AB2" s="3" t="s">
+      <c r="AC2" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="AC2" s="3" t="s">
+      <c r="AD2" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="AD2" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="AF2">
         <v>2010</v>
@@ -2711,7 +2773,19 @@
         <v>110.4</v>
       </c>
       <c r="AA6" s="2">
-        <v>95</v>
+        <v>102</v>
+      </c>
+      <c r="AB6" s="2">
+        <f>+AA6+5</f>
+        <v>107</v>
+      </c>
+      <c r="AC6" s="2">
+        <f>+AB6+5</f>
+        <v>112</v>
+      </c>
+      <c r="AD6" s="2">
+        <f>+AC6+5</f>
+        <v>117</v>
       </c>
       <c r="AS6" s="2">
         <f>SUM(O6:R6)</f>
@@ -2726,8 +2800,8 @@
         <v>898.75099999999998</v>
       </c>
       <c r="AV6" s="2">
-        <f>SUM(W6:Z6)</f>
-        <v>898.75099999999998</v>
+        <f>SUM(AA6:AD6)</f>
+        <v>438</v>
       </c>
       <c r="AW6" s="2">
         <v>100</v>
@@ -2812,7 +2886,19 @@
         <v>259.2</v>
       </c>
       <c r="AA7" s="2">
-        <v>226</v>
+        <v>228.6</v>
+      </c>
+      <c r="AB7" s="2">
+        <f>+AA7</f>
+        <v>228.6</v>
+      </c>
+      <c r="AC7" s="2">
+        <f>+AB7</f>
+        <v>228.6</v>
+      </c>
+      <c r="AD7" s="2">
+        <f>+AC7</f>
+        <v>228.6</v>
       </c>
       <c r="AL7" s="2">
         <f t="shared" ref="AL7:AR7" si="15">+AL13</f>
@@ -2855,44 +2941,44 @@
         <v>965.97199999999998</v>
       </c>
       <c r="AV7" s="2">
-        <f>SUM(W7:Z7)</f>
-        <v>965.97199999999998</v>
+        <f>SUM(AA7:AD7)</f>
+        <v>914.4</v>
       </c>
       <c r="AW7" s="2">
         <f t="shared" ref="AW7:BE7" si="19">+AV7*0.99</f>
-        <v>956.31227999999999</v>
+        <v>905.25599999999997</v>
       </c>
       <c r="AX7" s="2">
         <f t="shared" si="19"/>
-        <v>946.74915720000001</v>
+        <v>896.20344</v>
       </c>
       <c r="AY7" s="2">
         <f t="shared" si="19"/>
-        <v>937.28166562800004</v>
+        <v>887.24140560000001</v>
       </c>
       <c r="AZ7" s="2">
         <f t="shared" si="19"/>
-        <v>927.90884897171998</v>
+        <v>878.36899154399998</v>
       </c>
       <c r="BA7" s="2">
         <f t="shared" si="19"/>
-        <v>918.62976048200278</v>
+        <v>869.58530162855993</v>
       </c>
       <c r="BB7" s="2">
         <f t="shared" si="19"/>
-        <v>909.4434628771827</v>
+        <v>860.88944861227435</v>
       </c>
       <c r="BC7" s="2">
         <f t="shared" si="19"/>
-        <v>900.34902824841083</v>
+        <v>852.28055412615163</v>
       </c>
       <c r="BD7" s="2">
         <f t="shared" si="19"/>
-        <v>891.34553796592672</v>
+        <v>843.75774858489012</v>
       </c>
       <c r="BE7" s="2">
         <f t="shared" si="19"/>
-        <v>882.43208258626748</v>
+        <v>835.3201710990412</v>
       </c>
     </row>
     <row r="8" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3038,7 +3124,19 @@
       </c>
       <c r="AA11" s="2">
         <f>+AA7+AA6</f>
-        <v>321</v>
+        <v>330.6</v>
+      </c>
+      <c r="AB11" s="2">
+        <f>+AB7+AB6</f>
+        <v>335.6</v>
+      </c>
+      <c r="AC11" s="2">
+        <f>+AC7+AC6</f>
+        <v>340.6</v>
+      </c>
+      <c r="AD11" s="2">
+        <f>+AD7+AD6</f>
+        <v>345.6</v>
       </c>
       <c r="AS11" s="2">
         <f t="shared" ref="AS11:AT11" si="20">+AS7+AS6</f>
@@ -3054,43 +3152,43 @@
       </c>
       <c r="AV11" s="2">
         <f t="shared" ref="AV11:BE11" si="21">+AV7+AV6</f>
-        <v>1864.723</v>
+        <v>1352.4</v>
       </c>
       <c r="AW11" s="2">
         <f t="shared" si="21"/>
-        <v>1056.3122800000001</v>
+        <v>1005.256</v>
       </c>
       <c r="AX11" s="2">
         <f t="shared" si="21"/>
-        <v>1096.7491571999999</v>
+        <v>1046.20344</v>
       </c>
       <c r="AY11" s="2">
         <f t="shared" si="21"/>
-        <v>1137.2816656280002</v>
+        <v>1087.2414056</v>
       </c>
       <c r="AZ11" s="2">
         <f t="shared" si="21"/>
-        <v>1177.9088489717201</v>
+        <v>1128.368991544</v>
       </c>
       <c r="BA11" s="2">
         <f t="shared" si="21"/>
-        <v>1218.6297604820029</v>
+        <v>1169.58530162856</v>
       </c>
       <c r="BB11" s="2">
         <f t="shared" si="21"/>
-        <v>1209.4434628771828</v>
+        <v>1160.8894486122745</v>
       </c>
       <c r="BC11" s="2">
         <f t="shared" si="21"/>
-        <v>1200.3490282484108</v>
+        <v>1152.2805541261516</v>
       </c>
       <c r="BD11" s="2">
         <f t="shared" si="21"/>
-        <v>1191.3455379659267</v>
+        <v>1143.7577485848901</v>
       </c>
       <c r="BE11" s="2">
         <f t="shared" si="21"/>
-        <v>1182.4320825862674</v>
+        <v>1135.3201710990411</v>
       </c>
     </row>
     <row r="12" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3152,7 +3250,17 @@
         <v>73.326999999999998</v>
       </c>
       <c r="AA12" s="2">
-        <v>50</v>
+        <f>400.288-40-253</f>
+        <v>107.28800000000001</v>
+      </c>
+      <c r="AB12" s="2">
+        <v>30</v>
+      </c>
+      <c r="AC12" s="2">
+        <v>30</v>
+      </c>
+      <c r="AD12" s="2">
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:57" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.3">
@@ -3230,19 +3338,19 @@
       </c>
       <c r="AA13" s="6">
         <f>+AA11+AA12</f>
-        <v>371</v>
+        <v>437.88800000000003</v>
       </c>
       <c r="AB13" s="6">
         <f>+AB11+AB12</f>
-        <v>0</v>
+        <v>365.6</v>
       </c>
       <c r="AC13" s="6">
         <f>+AC11+AC12</f>
-        <v>0</v>
+        <v>370.6</v>
       </c>
       <c r="AD13" s="6">
         <f>+AD11+AD12</f>
-        <v>0</v>
+        <v>375.6</v>
       </c>
       <c r="AL13" s="6">
         <v>5.4</v>
@@ -3279,43 +3387,43 @@
       </c>
       <c r="AV13" s="6">
         <f t="shared" ref="AV13:BE13" si="24">+AV11+AV12</f>
-        <v>1864.723</v>
+        <v>1352.4</v>
       </c>
       <c r="AW13" s="6">
         <f t="shared" si="24"/>
-        <v>1056.3122800000001</v>
+        <v>1005.256</v>
       </c>
       <c r="AX13" s="6">
         <f t="shared" si="24"/>
-        <v>1096.7491571999999</v>
+        <v>1046.20344</v>
       </c>
       <c r="AY13" s="6">
         <f t="shared" si="24"/>
-        <v>1137.2816656280002</v>
+        <v>1087.2414056</v>
       </c>
       <c r="AZ13" s="6">
         <f t="shared" si="24"/>
-        <v>1177.9088489717201</v>
+        <v>1128.368991544</v>
       </c>
       <c r="BA13" s="6">
         <f t="shared" si="24"/>
-        <v>1218.6297604820029</v>
+        <v>1169.58530162856</v>
       </c>
       <c r="BB13" s="6">
         <f t="shared" si="24"/>
-        <v>1209.4434628771828</v>
+        <v>1160.8894486122745</v>
       </c>
       <c r="BC13" s="6">
         <f t="shared" si="24"/>
-        <v>1200.3490282484108</v>
+        <v>1152.2805541261516</v>
       </c>
       <c r="BD13" s="6">
         <f t="shared" si="24"/>
-        <v>1191.3455379659267</v>
+        <v>1143.7577485848901</v>
       </c>
       <c r="BE13" s="6">
         <f t="shared" si="24"/>
-        <v>1182.4320825862674</v>
+        <v>1135.3201710990411</v>
       </c>
     </row>
     <row r="14" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3377,6 +3485,21 @@
         <f>+Z13*0.18</f>
         <v>79.726860000000002</v>
       </c>
+      <c r="AA14" s="2">
+        <v>108.768</v>
+      </c>
+      <c r="AB14" s="2">
+        <f>+AB13-AB15</f>
+        <v>91.399999999999977</v>
+      </c>
+      <c r="AC14" s="2">
+        <f>+AC13-AC15</f>
+        <v>92.649999999999977</v>
+      </c>
+      <c r="AD14" s="2">
+        <f>+AD13-AD15</f>
+        <v>93.899999999999977</v>
+      </c>
       <c r="AS14" s="2">
         <f t="shared" ref="AS14:AS17" si="25">SUM(O14:R14)</f>
         <v>150.34300000000002</v>
@@ -3391,43 +3514,43 @@
       </c>
       <c r="AV14" s="2">
         <f>+AV13-AV15</f>
-        <v>279.70845000000008</v>
+        <v>202.86000000000013</v>
       </c>
       <c r="AW14" s="2">
         <f t="shared" ref="AW14:BE14" si="28">+AW13-AW15</f>
-        <v>158.44684200000006</v>
+        <v>150.78840000000002</v>
       </c>
       <c r="AX14" s="2">
         <f t="shared" si="28"/>
-        <v>164.51237358000003</v>
+        <v>156.93051600000001</v>
       </c>
       <c r="AY14" s="2">
         <f t="shared" si="28"/>
-        <v>170.59224984420007</v>
+        <v>163.08621084000004</v>
       </c>
       <c r="AZ14" s="2">
         <f t="shared" si="28"/>
-        <v>176.68632734575806</v>
+        <v>169.25534873160007</v>
       </c>
       <c r="BA14" s="2">
         <f t="shared" si="28"/>
-        <v>182.79446407230057</v>
+        <v>175.43779524428408</v>
       </c>
       <c r="BB14" s="2">
         <f t="shared" si="28"/>
-        <v>181.4165194315774</v>
+        <v>174.13341729184117</v>
       </c>
       <c r="BC14" s="2">
         <f t="shared" si="28"/>
-        <v>180.05235423726162</v>
+        <v>172.8420831189228</v>
       </c>
       <c r="BD14" s="2">
         <f t="shared" si="28"/>
-        <v>178.70183069488905</v>
+        <v>171.56366228773356</v>
       </c>
       <c r="BE14" s="2">
         <f t="shared" si="28"/>
-        <v>177.36481238794011</v>
+        <v>170.29802566485614</v>
       </c>
     </row>
     <row r="15" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3503,6 +3626,22 @@
         <f t="shared" si="30"/>
         <v>363.20014000000003</v>
       </c>
+      <c r="AA15" s="2">
+        <f>+AA13-AA14</f>
+        <v>329.12</v>
+      </c>
+      <c r="AB15" s="2">
+        <f>+AB13*0.75</f>
+        <v>274.20000000000005</v>
+      </c>
+      <c r="AC15" s="2">
+        <f>+AC13*0.75</f>
+        <v>277.95000000000005</v>
+      </c>
+      <c r="AD15" s="2">
+        <f>+AD13*0.75</f>
+        <v>281.70000000000005</v>
+      </c>
       <c r="AS15" s="2">
         <f>+AS13-AS14</f>
         <v>994.5329999999999</v>
@@ -3517,43 +3656,43 @@
       </c>
       <c r="AV15" s="2">
         <f>+AV13*0.85</f>
-        <v>1585.0145499999999</v>
+        <v>1149.54</v>
       </c>
       <c r="AW15" s="2">
         <f t="shared" ref="AW15:BE15" si="31">+AW13*0.85</f>
-        <v>897.86543800000004</v>
+        <v>854.46759999999995</v>
       </c>
       <c r="AX15" s="2">
         <f t="shared" si="31"/>
-        <v>932.23678361999987</v>
+        <v>889.27292399999999</v>
       </c>
       <c r="AY15" s="2">
         <f t="shared" si="31"/>
-        <v>966.68941578380009</v>
+        <v>924.15519475999997</v>
       </c>
       <c r="AZ15" s="2">
         <f t="shared" si="31"/>
-        <v>1001.222521625962</v>
+        <v>959.11364281239992</v>
       </c>
       <c r="BA15" s="2">
         <f t="shared" si="31"/>
-        <v>1035.8352964097023</v>
+        <v>994.14750638427597</v>
       </c>
       <c r="BB15" s="2">
         <f t="shared" si="31"/>
-        <v>1028.0269434456054</v>
+        <v>986.75603132043329</v>
       </c>
       <c r="BC15" s="2">
         <f t="shared" si="31"/>
-        <v>1020.2966740111492</v>
+        <v>979.43847100722883</v>
       </c>
       <c r="BD15" s="2">
         <f t="shared" si="31"/>
-        <v>1012.6437072710377</v>
+        <v>972.19408629715656</v>
       </c>
       <c r="BE15" s="2">
         <f t="shared" si="31"/>
-        <v>1005.0672701983273</v>
+        <v>965.02214543418495</v>
       </c>
     </row>
     <row r="16" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3615,6 +3754,22 @@
       <c r="Z16" s="2">
         <v>325.33600000000001</v>
       </c>
+      <c r="AA16" s="2">
+        <f>153.96-6.206</f>
+        <v>147.75400000000002</v>
+      </c>
+      <c r="AB16" s="2">
+        <f>+AA16-2</f>
+        <v>145.75400000000002</v>
+      </c>
+      <c r="AC16" s="2">
+        <f t="shared" ref="AC16:AD16" si="32">+AB16-2</f>
+        <v>143.75400000000002</v>
+      </c>
+      <c r="AD16" s="2">
+        <f t="shared" si="32"/>
+        <v>141.75400000000002</v>
+      </c>
       <c r="AS16" s="2">
         <f t="shared" si="25"/>
         <v>877.38699999999994</v>
@@ -3624,7 +3779,7 @@
         <v>780.20299999999997</v>
       </c>
     </row>
-    <row r="17" spans="2:60" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:75" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>27</v>
       </c>
@@ -3682,6 +3837,22 @@
       <c r="Z17" s="2">
         <v>128.297</v>
       </c>
+      <c r="AA17" s="2">
+        <f>108.951-3.697</f>
+        <v>105.25399999999999</v>
+      </c>
+      <c r="AB17" s="2">
+        <f t="shared" ref="AB17:AD17" si="33">+AA17-2</f>
+        <v>103.25399999999999</v>
+      </c>
+      <c r="AC17" s="2">
+        <f t="shared" si="33"/>
+        <v>101.25399999999999</v>
+      </c>
+      <c r="AD17" s="2">
+        <f t="shared" si="33"/>
+        <v>99.253999999999991</v>
+      </c>
       <c r="AS17" s="2">
         <f t="shared" si="25"/>
         <v>481.87099999999998</v>
@@ -3699,43 +3870,43 @@
         <v>502.62479999999999</v>
       </c>
       <c r="AW17" s="2">
-        <f t="shared" ref="AW17:BE17" si="32">+AV17*0.9</f>
+        <f t="shared" ref="AW17:BE17" si="34">+AV17*0.9</f>
         <v>452.36232000000001</v>
       </c>
       <c r="AX17" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>407.12608800000004</v>
       </c>
       <c r="AY17" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>366.41347920000004</v>
       </c>
       <c r="AZ17" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>329.77213128000005</v>
       </c>
       <c r="BA17" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>296.79491815200004</v>
       </c>
       <c r="BB17" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>267.11542633680006</v>
       </c>
       <c r="BC17" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>240.40388370312004</v>
       </c>
       <c r="BD17" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>216.36349533280804</v>
       </c>
       <c r="BE17" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>194.72714579952725</v>
       </c>
     </row>
-    <row r="18" spans="2:60" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:75" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>22</v>
       </c>
@@ -3769,7 +3940,7 @@
         <v>360.45399999999995</v>
       </c>
       <c r="Q18" s="2">
-        <f t="shared" ref="Q18" si="33">+Q16+Q17</f>
+        <f t="shared" ref="Q18" si="35">+Q16+Q17</f>
         <v>315.19399999999996</v>
       </c>
       <c r="R18" s="2">
@@ -3785,7 +3956,7 @@
         <v>318.48599999999999</v>
       </c>
       <c r="U18" s="2">
-        <f t="shared" ref="U18" si="34">+U16+U17</f>
+        <f t="shared" ref="U18" si="36">+U16+U17</f>
         <v>351.28300000000002</v>
       </c>
       <c r="V18" s="2">
@@ -3808,6 +3979,22 @@
         <f>+Z17+Z16</f>
         <v>453.63300000000004</v>
       </c>
+      <c r="AA18" s="2">
+        <f>+AA17+AA16</f>
+        <v>253.00800000000001</v>
+      </c>
+      <c r="AB18" s="2">
+        <f t="shared" ref="AB18:AD18" si="37">+AB17+AB16</f>
+        <v>249.00800000000001</v>
+      </c>
+      <c r="AC18" s="2">
+        <f t="shared" si="37"/>
+        <v>245.00800000000001</v>
+      </c>
+      <c r="AD18" s="2">
+        <f t="shared" si="37"/>
+        <v>241.00800000000001</v>
+      </c>
       <c r="AS18" s="2">
         <f>+AS16+AS17</f>
         <v>1359.2579999999998</v>
@@ -3821,47 +4008,47 @@
         <v>558.47199999999998</v>
       </c>
       <c r="AV18" s="2">
-        <f t="shared" ref="AV18" si="35">+AV16+AV17</f>
+        <f t="shared" ref="AV18" si="38">+AV16+AV17</f>
         <v>502.62479999999999</v>
       </c>
       <c r="AW18" s="2">
-        <f t="shared" ref="AW18" si="36">+AW16+AW17</f>
+        <f t="shared" ref="AW18" si="39">+AW16+AW17</f>
         <v>452.36232000000001</v>
       </c>
       <c r="AX18" s="2">
-        <f t="shared" ref="AX18" si="37">+AX16+AX17</f>
+        <f t="shared" ref="AX18" si="40">+AX16+AX17</f>
         <v>407.12608800000004</v>
       </c>
       <c r="AY18" s="2">
-        <f t="shared" ref="AY18" si="38">+AY16+AY17</f>
+        <f t="shared" ref="AY18" si="41">+AY16+AY17</f>
         <v>366.41347920000004</v>
       </c>
       <c r="AZ18" s="2">
-        <f t="shared" ref="AZ18" si="39">+AZ16+AZ17</f>
+        <f t="shared" ref="AZ18" si="42">+AZ16+AZ17</f>
         <v>329.77213128000005</v>
       </c>
       <c r="BA18" s="2">
-        <f t="shared" ref="BA18" si="40">+BA16+BA17</f>
+        <f t="shared" ref="BA18" si="43">+BA16+BA17</f>
         <v>296.79491815200004</v>
       </c>
       <c r="BB18" s="2">
-        <f t="shared" ref="BB18" si="41">+BB16+BB17</f>
+        <f t="shared" ref="BB18" si="44">+BB16+BB17</f>
         <v>267.11542633680006</v>
       </c>
       <c r="BC18" s="2">
-        <f t="shared" ref="BC18" si="42">+BC16+BC17</f>
+        <f t="shared" ref="BC18" si="45">+BC16+BC17</f>
         <v>240.40388370312004</v>
       </c>
       <c r="BD18" s="2">
-        <f t="shared" ref="BD18" si="43">+BD16+BD17</f>
+        <f t="shared" ref="BD18" si="46">+BD16+BD17</f>
         <v>216.36349533280804</v>
       </c>
       <c r="BE18" s="2">
-        <f t="shared" ref="BE18" si="44">+BE16+BE17</f>
+        <f t="shared" ref="BE18" si="47">+BE16+BE17</f>
         <v>194.72714579952725</v>
       </c>
     </row>
-    <row r="19" spans="2:60" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:75" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>23</v>
       </c>
@@ -3895,7 +4082,7 @@
         <v>-133.33999999999995</v>
       </c>
       <c r="Q19" s="2">
-        <f t="shared" ref="Q19" si="45">+Q15-Q18</f>
+        <f t="shared" ref="Q19" si="48">+Q15-Q18</f>
         <v>-20.402999999999963</v>
       </c>
       <c r="R19" s="2">
@@ -3911,7 +4098,7 @@
         <v>-0.10000000000002274</v>
       </c>
       <c r="U19" s="2">
-        <f t="shared" ref="U19" si="46">+U15-U18</f>
+        <f t="shared" ref="U19" si="49">+U15-U18</f>
         <v>24.226999999999975</v>
       </c>
       <c r="V19" s="2">
@@ -3934,6 +4121,22 @@
         <f>+Z15-Z18</f>
         <v>-90.432860000000005</v>
       </c>
+      <c r="AA19" s="2">
+        <f>+AA15-AA18</f>
+        <v>76.111999999999995</v>
+      </c>
+      <c r="AB19" s="2">
+        <f t="shared" ref="AB19:AD19" si="50">+AB15-AB18</f>
+        <v>25.192000000000036</v>
+      </c>
+      <c r="AC19" s="2">
+        <f t="shared" si="50"/>
+        <v>32.942000000000036</v>
+      </c>
+      <c r="AD19" s="2">
+        <f t="shared" si="50"/>
+        <v>40.692000000000036</v>
+      </c>
       <c r="AS19" s="2">
         <f>+AS15-AS18</f>
         <v>-364.72499999999991</v>
@@ -3947,47 +4150,47 @@
         <v>785.62714000000005</v>
       </c>
       <c r="AV19" s="2">
-        <f t="shared" ref="AV19" si="47">+AV15-AV18</f>
-        <v>1082.3897499999998</v>
+        <f t="shared" ref="AV19" si="51">+AV15-AV18</f>
+        <v>646.91519999999991</v>
       </c>
       <c r="AW19" s="2">
-        <f t="shared" ref="AW19" si="48">+AW15-AW18</f>
-        <v>445.50311800000003</v>
+        <f t="shared" ref="AW19" si="52">+AW15-AW18</f>
+        <v>402.10527999999994</v>
       </c>
       <c r="AX19" s="2">
-        <f t="shared" ref="AX19" si="49">+AX15-AX18</f>
-        <v>525.11069561999989</v>
+        <f t="shared" ref="AX19" si="53">+AX15-AX18</f>
+        <v>482.14683599999995</v>
       </c>
       <c r="AY19" s="2">
-        <f t="shared" ref="AY19" si="50">+AY15-AY18</f>
-        <v>600.2759365838001</v>
+        <f t="shared" ref="AY19" si="54">+AY15-AY18</f>
+        <v>557.74171555999988</v>
       </c>
       <c r="AZ19" s="2">
-        <f t="shared" ref="AZ19" si="51">+AZ15-AZ18</f>
-        <v>671.45039034596198</v>
+        <f t="shared" ref="AZ19" si="55">+AZ15-AZ18</f>
+        <v>629.34151153239986</v>
       </c>
       <c r="BA19" s="2">
-        <f t="shared" ref="BA19" si="52">+BA15-BA18</f>
-        <v>739.04037825770229</v>
+        <f t="shared" ref="BA19" si="56">+BA15-BA18</f>
+        <v>697.35258823227593</v>
       </c>
       <c r="BB19" s="2">
-        <f t="shared" ref="BB19" si="53">+BB15-BB18</f>
-        <v>760.91151710880536</v>
+        <f t="shared" ref="BB19" si="57">+BB15-BB18</f>
+        <v>719.64060498363324</v>
       </c>
       <c r="BC19" s="2">
-        <f t="shared" ref="BC19" si="54">+BC15-BC18</f>
-        <v>779.89279030802913</v>
+        <f t="shared" ref="BC19" si="58">+BC15-BC18</f>
+        <v>739.03458730410875</v>
       </c>
       <c r="BD19" s="2">
-        <f t="shared" ref="BD19" si="55">+BD15-BD18</f>
-        <v>796.28021193822963</v>
+        <f t="shared" ref="BD19" si="59">+BD15-BD18</f>
+        <v>755.83059096434852</v>
       </c>
       <c r="BE19" s="2">
-        <f t="shared" ref="BE19" si="56">+BE15-BE18</f>
-        <v>810.34012439880007</v>
-      </c>
-    </row>
-    <row r="20" spans="2:60" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <f t="shared" ref="BE19" si="60">+BE15-BE18</f>
+        <v>770.29499963465764</v>
+      </c>
+    </row>
+    <row r="20" spans="2:75" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>28</v>
       </c>
@@ -4045,16 +4248,28 @@
       <c r="Z20" s="2">
         <v>0</v>
       </c>
+      <c r="AA20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="2">
+        <v>0</v>
+      </c>
       <c r="AS20" s="2">
-        <f t="shared" ref="AS20" si="57">SUM(O20:R20)</f>
+        <f t="shared" ref="AS20" si="61">SUM(O20:R20)</f>
         <v>33.055</v>
       </c>
       <c r="AT20" s="2">
-        <f t="shared" ref="AT20" si="58">SUM(S20:V20)</f>
+        <f t="shared" ref="AT20" si="62">SUM(S20:V20)</f>
         <v>42.692999999999998</v>
       </c>
     </row>
-    <row r="21" spans="2:60" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:75" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>29</v>
       </c>
@@ -4072,39 +4287,39 @@
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
       <c r="M21" s="5">
-        <f t="shared" ref="M21:U21" si="59">+M19+M20</f>
+        <f t="shared" ref="M21:U21" si="63">+M19+M20</f>
         <v>-137.49900000000002</v>
       </c>
       <c r="N21" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>-101.12699999999997</v>
       </c>
       <c r="O21" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>-125.20300000000003</v>
       </c>
       <c r="P21" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>-116.40599999999995</v>
       </c>
       <c r="Q21" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>-32.734999999999964</v>
       </c>
       <c r="R21" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>41.134000000000036</v>
       </c>
       <c r="S21" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>64.367999999999995</v>
       </c>
       <c r="T21" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>14.177999999999978</v>
       </c>
       <c r="U21" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>36.036999999999978</v>
       </c>
       <c r="V21" s="2">
@@ -4127,6 +4342,22 @@
         <f>+Z19+Z20</f>
         <v>-90.432860000000005</v>
       </c>
+      <c r="AA21" s="2">
+        <f>+AA19+AA20</f>
+        <v>76.111999999999995</v>
+      </c>
+      <c r="AB21" s="2">
+        <f t="shared" ref="AB21:AD21" si="64">+AB19+AB20</f>
+        <v>25.192000000000036</v>
+      </c>
+      <c r="AC21" s="2">
+        <f t="shared" si="64"/>
+        <v>32.942000000000036</v>
+      </c>
+      <c r="AD21" s="2">
+        <f t="shared" si="64"/>
+        <v>40.692000000000036</v>
+      </c>
       <c r="AS21" s="2">
         <f>+AS19+AS20</f>
         <v>-331.6699999999999</v>
@@ -4140,47 +4371,47 @@
         <v>785.62714000000005</v>
       </c>
       <c r="AV21" s="2">
-        <f t="shared" ref="AV21:BE21" si="60">+AV19+AV20</f>
-        <v>1082.3897499999998</v>
+        <f t="shared" ref="AV21:BE21" si="65">+AV19+AV20</f>
+        <v>646.91519999999991</v>
       </c>
       <c r="AW21" s="2">
-        <f t="shared" si="60"/>
-        <v>445.50311800000003</v>
+        <f t="shared" si="65"/>
+        <v>402.10527999999994</v>
       </c>
       <c r="AX21" s="2">
-        <f t="shared" si="60"/>
-        <v>525.11069561999989</v>
+        <f t="shared" si="65"/>
+        <v>482.14683599999995</v>
       </c>
       <c r="AY21" s="2">
-        <f t="shared" si="60"/>
-        <v>600.2759365838001</v>
+        <f t="shared" si="65"/>
+        <v>557.74171555999988</v>
       </c>
       <c r="AZ21" s="2">
-        <f t="shared" si="60"/>
-        <v>671.45039034596198</v>
+        <f t="shared" si="65"/>
+        <v>629.34151153239986</v>
       </c>
       <c r="BA21" s="2">
-        <f t="shared" si="60"/>
-        <v>739.04037825770229</v>
+        <f t="shared" si="65"/>
+        <v>697.35258823227593</v>
       </c>
       <c r="BB21" s="2">
-        <f t="shared" si="60"/>
-        <v>760.91151710880536</v>
+        <f t="shared" si="65"/>
+        <v>719.64060498363324</v>
       </c>
       <c r="BC21" s="2">
-        <f t="shared" si="60"/>
-        <v>779.89279030802913</v>
+        <f t="shared" si="65"/>
+        <v>739.03458730410875</v>
       </c>
       <c r="BD21" s="2">
-        <f t="shared" si="60"/>
-        <v>796.28021193822963</v>
+        <f t="shared" si="65"/>
+        <v>755.83059096434852</v>
       </c>
       <c r="BE21" s="2">
-        <f t="shared" si="60"/>
-        <v>810.34012439880007</v>
-      </c>
-    </row>
-    <row r="22" spans="2:60" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="65"/>
+        <v>770.29499963465764</v>
+      </c>
+    </row>
+    <row r="22" spans="2:75" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>30</v>
       </c>
@@ -4238,12 +4469,24 @@
       <c r="Z22" s="2">
         <v>4</v>
       </c>
+      <c r="AA22" s="2">
+        <v>12.215</v>
+      </c>
+      <c r="AB22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="2">
+        <v>0</v>
+      </c>
       <c r="AS22" s="2">
-        <f t="shared" ref="AS22" si="61">SUM(O22:R22)</f>
+        <f t="shared" ref="AS22" si="66">SUM(O22:R22)</f>
         <v>15.879000000000001</v>
       </c>
       <c r="AT22" s="2">
-        <f t="shared" ref="AT22" si="62">SUM(S22:V22)</f>
+        <f t="shared" ref="AT22" si="67">SUM(S22:V22)</f>
         <v>25.535</v>
       </c>
       <c r="AU22" s="2">
@@ -4251,47 +4494,47 @@
         <v>157.12542800000003</v>
       </c>
       <c r="AV22" s="2">
-        <f t="shared" ref="AV22:BE22" si="63">+AV21*0.2</f>
-        <v>216.47794999999996</v>
+        <f t="shared" ref="AV22:BE22" si="68">+AV21*0.2</f>
+        <v>129.38303999999999</v>
       </c>
       <c r="AW22" s="2">
-        <f t="shared" si="63"/>
-        <v>89.100623600000006</v>
+        <f t="shared" si="68"/>
+        <v>80.421055999999993</v>
       </c>
       <c r="AX22" s="2">
-        <f t="shared" si="63"/>
-        <v>105.02213912399998</v>
+        <f t="shared" si="68"/>
+        <v>96.429367200000002</v>
       </c>
       <c r="AY22" s="2">
-        <f t="shared" si="63"/>
-        <v>120.05518731676003</v>
+        <f t="shared" si="68"/>
+        <v>111.54834311199998</v>
       </c>
       <c r="AZ22" s="2">
-        <f t="shared" si="63"/>
-        <v>134.29007806919239</v>
+        <f t="shared" si="68"/>
+        <v>125.86830230647998</v>
       </c>
       <c r="BA22" s="2">
-        <f t="shared" si="63"/>
-        <v>147.80807565154046</v>
+        <f t="shared" si="68"/>
+        <v>139.47051764645519</v>
       </c>
       <c r="BB22" s="2">
-        <f t="shared" si="63"/>
-        <v>152.18230342176108</v>
+        <f t="shared" si="68"/>
+        <v>143.92812099672665</v>
       </c>
       <c r="BC22" s="2">
-        <f t="shared" si="63"/>
-        <v>155.97855806160584</v>
+        <f t="shared" si="68"/>
+        <v>147.80691746082175</v>
       </c>
       <c r="BD22" s="2">
-        <f t="shared" si="63"/>
-        <v>159.25604238764595</v>
+        <f t="shared" si="68"/>
+        <v>151.1661181928697</v>
       </c>
       <c r="BE22" s="2">
-        <f t="shared" si="63"/>
-        <v>162.06802487976003</v>
-      </c>
-    </row>
-    <row r="23" spans="2:60" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="68"/>
+        <v>154.05899992693153</v>
+      </c>
+    </row>
+    <row r="23" spans="2:75" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>31</v>
       </c>
@@ -4309,39 +4552,39 @@
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
       <c r="M23" s="5">
-        <f t="shared" ref="M23:U23" si="64">+M21-M22</f>
+        <f t="shared" ref="M23:U23" si="69">+M21-M22</f>
         <v>-137.49900000000002</v>
       </c>
       <c r="N23" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>-109.06499999999997</v>
       </c>
       <c r="O23" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>-129.24800000000002</v>
       </c>
       <c r="P23" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>-125.76099999999995</v>
       </c>
       <c r="Q23" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>-40.497999999999962</v>
       </c>
       <c r="R23" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>46.418000000000035</v>
       </c>
       <c r="S23" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>59.038999999999994</v>
       </c>
       <c r="T23" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>7.0609999999999777</v>
       </c>
       <c r="U23" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>35.641999999999975</v>
       </c>
       <c r="V23" s="2">
@@ -4364,6 +4607,22 @@
         <f>+Z21-Z22</f>
         <v>-94.432860000000005</v>
       </c>
+      <c r="AA23" s="2">
+        <f>+AA21-AA22</f>
+        <v>63.896999999999991</v>
+      </c>
+      <c r="AB23" s="2">
+        <f t="shared" ref="AB23:AD23" si="70">+AB21-AB22</f>
+        <v>25.192000000000036</v>
+      </c>
+      <c r="AC23" s="2">
+        <f t="shared" si="70"/>
+        <v>32.942000000000036</v>
+      </c>
+      <c r="AD23" s="2">
+        <f t="shared" si="70"/>
+        <v>40.692000000000036</v>
+      </c>
       <c r="AS23" s="2">
         <f>+AS21-AS22</f>
         <v>-347.54899999999992</v>
@@ -4377,47 +4636,119 @@
         <v>628.501712</v>
       </c>
       <c r="AV23" s="2">
-        <f t="shared" ref="AV23:BE23" si="65">+AV21-AV22</f>
-        <v>865.91179999999986</v>
+        <f t="shared" ref="AV23:BE23" si="71">+AV21-AV22</f>
+        <v>517.53215999999998</v>
       </c>
       <c r="AW23" s="2">
-        <f t="shared" si="65"/>
-        <v>356.40249440000002</v>
+        <f t="shared" si="71"/>
+        <v>321.68422399999997</v>
       </c>
       <c r="AX23" s="2">
-        <f t="shared" si="65"/>
-        <v>420.08855649599991</v>
+        <f t="shared" si="71"/>
+        <v>385.71746879999995</v>
       </c>
       <c r="AY23" s="2">
-        <f t="shared" si="65"/>
-        <v>480.22074926704011</v>
+        <f t="shared" si="71"/>
+        <v>446.19337244799988</v>
       </c>
       <c r="AZ23" s="2">
-        <f t="shared" si="65"/>
-        <v>537.16031227676956</v>
+        <f t="shared" si="71"/>
+        <v>503.4732092259199</v>
       </c>
       <c r="BA23" s="2">
-        <f t="shared" si="65"/>
-        <v>591.23230260616185</v>
+        <f t="shared" si="71"/>
+        <v>557.88207058582077</v>
       </c>
       <c r="BB23" s="2">
-        <f t="shared" si="65"/>
-        <v>608.72921368704431</v>
+        <f t="shared" si="71"/>
+        <v>575.71248398690659</v>
       </c>
       <c r="BC23" s="2">
-        <f t="shared" si="65"/>
-        <v>623.91423224642335</v>
+        <f t="shared" si="71"/>
+        <v>591.227669843287</v>
       </c>
       <c r="BD23" s="2">
-        <f t="shared" si="65"/>
-        <v>637.02416955058368</v>
+        <f t="shared" si="71"/>
+        <v>604.66447277147881</v>
       </c>
       <c r="BE23" s="2">
-        <f t="shared" si="65"/>
-        <v>648.27209951904001</v>
-      </c>
-    </row>
-    <row r="24" spans="2:60" x14ac:dyDescent="0.25">
+        <f t="shared" si="71"/>
+        <v>616.23599970772614</v>
+      </c>
+      <c r="BF23" s="2">
+        <f>+BE23*(1+$BH$27)</f>
+        <v>462.17699978079463</v>
+      </c>
+      <c r="BG23" s="2">
+        <f>+BF23*(1+$BH$27)</f>
+        <v>346.63274983559597</v>
+      </c>
+      <c r="BH23" s="2">
+        <f>+BG23*(1+$BH$27)</f>
+        <v>259.97456237669701</v>
+      </c>
+      <c r="BI23" s="2">
+        <f>+BH23*(1+$BH$27)</f>
+        <v>194.98092178252276</v>
+      </c>
+      <c r="BJ23" s="2">
+        <f t="shared" ref="BJ23:BW23" si="72">+BI23*(1+$BH$27)</f>
+        <v>146.23569133689207</v>
+      </c>
+      <c r="BK23" s="2">
+        <f t="shared" si="72"/>
+        <v>109.67676850266906</v>
+      </c>
+      <c r="BL23" s="2">
+        <f t="shared" si="72"/>
+        <v>82.257576377001797</v>
+      </c>
+      <c r="BM23" s="2">
+        <f t="shared" si="72"/>
+        <v>61.693182282751351</v>
+      </c>
+      <c r="BN23" s="2">
+        <f t="shared" si="72"/>
+        <v>46.26988671206351</v>
+      </c>
+      <c r="BO23" s="2">
+        <f t="shared" si="72"/>
+        <v>34.702415034047633</v>
+      </c>
+      <c r="BP23" s="2">
+        <f t="shared" si="72"/>
+        <v>26.026811275535724</v>
+      </c>
+      <c r="BQ23" s="2">
+        <f t="shared" si="72"/>
+        <v>19.520108456651794</v>
+      </c>
+      <c r="BR23" s="2">
+        <f t="shared" si="72"/>
+        <v>14.640081342488845</v>
+      </c>
+      <c r="BS23" s="2">
+        <f t="shared" si="72"/>
+        <v>10.980061006866634</v>
+      </c>
+      <c r="BT23" s="2">
+        <f t="shared" si="72"/>
+        <v>8.2350457551499758</v>
+      </c>
+      <c r="BU23" s="2">
+        <f t="shared" si="72"/>
+        <v>6.1762843163624819</v>
+      </c>
+      <c r="BV23" s="2">
+        <f t="shared" si="72"/>
+        <v>4.632213237271861</v>
+      </c>
+      <c r="BW23" s="2">
+        <f t="shared" si="72"/>
+        <v>3.4741599279538957</v>
+      </c>
+    </row>
+    <row r="24" spans="2:75" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>32</v>
       </c>
@@ -4426,111 +4757,123 @@
         <v>-0.68764396594892341</v>
       </c>
       <c r="M24" s="8">
-        <f t="shared" ref="M24:Z24" si="66">+M23/M25</f>
+        <f t="shared" ref="M24:AD24" si="73">+M23/M25</f>
         <v>-1.5691217419089791</v>
       </c>
       <c r="N24" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="73"/>
         <v>-1.2416607846262435</v>
       </c>
       <c r="O24" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="73"/>
         <v>-1.4656294649944437</v>
       </c>
       <c r="P24" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="73"/>
         <v>-1.4171371263085535</v>
       </c>
       <c r="Q24" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="73"/>
         <v>-0.45560193049758646</v>
       </c>
       <c r="R24" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="73"/>
         <v>0.43958937060817888</v>
       </c>
       <c r="S24" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="73"/>
         <v>0.59566761506951582</v>
       </c>
       <c r="T24" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="73"/>
         <v>7.1219640119422029E-2</v>
       </c>
       <c r="U24" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="73"/>
         <v>0.35483035998725687</v>
       </c>
       <c r="V24" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="73"/>
         <v>1.4721776646938443</v>
       </c>
       <c r="W24" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="73"/>
         <v>2.3108194161993385</v>
       </c>
       <c r="X24" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="73"/>
         <v>1.4472018232463917</v>
       </c>
       <c r="Y24" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="73"/>
         <v>-0.62097828147290957</v>
       </c>
       <c r="Z24" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="73"/>
         <v>-0.90113709885202253</v>
       </c>
-      <c r="AA24" s="1"/>
-      <c r="AB24" s="1"/>
-      <c r="AC24" s="1"/>
-      <c r="AD24" s="1"/>
+      <c r="AA24" s="1">
+        <f t="shared" si="73"/>
+        <v>0.52410676203287498</v>
+      </c>
+      <c r="AB24" s="1">
+        <f t="shared" si="73"/>
+        <v>0.20663407592112631</v>
+      </c>
+      <c r="AC24" s="1">
+        <f t="shared" si="73"/>
+        <v>0.27020243446307324</v>
+      </c>
+      <c r="AD24" s="1">
+        <f t="shared" si="73"/>
+        <v>0.33377079300502016</v>
+      </c>
       <c r="AU24" s="1">
         <f>+AU23/AU25</f>
         <v>5.7940309382893593</v>
       </c>
       <c r="AV24" s="1">
-        <f t="shared" ref="AV24:BE24" si="67">+AV23/AV25</f>
-        <v>7.9826668141674491</v>
+        <f t="shared" ref="AV24:BE24" si="74">+AV23/AV25</f>
+        <v>4.7710249460700256</v>
       </c>
       <c r="AW24" s="1">
-        <f t="shared" si="67"/>
-        <v>3.2856029500156723</v>
+        <f t="shared" si="74"/>
+        <v>2.9655421944429077</v>
       </c>
       <c r="AX24" s="1">
-        <f t="shared" si="67"/>
-        <v>3.8727119539797545</v>
+        <f t="shared" si="74"/>
+        <v>3.5558518059627184</v>
       </c>
       <c r="AY24" s="1">
-        <f t="shared" si="67"/>
-        <v>4.4270585510540785</v>
+        <f t="shared" si="74"/>
+        <v>4.1133670045172099</v>
       </c>
       <c r="AZ24" s="1">
-        <f t="shared" si="67"/>
-        <v>4.9519729361576923</v>
+        <f t="shared" si="74"/>
+        <v>4.6414183050861944</v>
       </c>
       <c r="BA24" s="1">
-        <f t="shared" si="67"/>
-        <v>5.4504517451754504</v>
+        <f t="shared" si="74"/>
+        <v>5.1430026604146688</v>
       </c>
       <c r="BB24" s="1">
-        <f t="shared" si="67"/>
-        <v>5.6117522511112732</v>
+        <f t="shared" si="74"/>
+        <v>5.3073776571980984</v>
       </c>
       <c r="BC24" s="1">
-        <f t="shared" si="67"/>
-        <v>5.7517398846398526</v>
+        <f t="shared" si="74"/>
+        <v>5.4504090366658096</v>
       </c>
       <c r="BD24" s="1">
-        <f t="shared" si="67"/>
-        <v>5.8725977612200495</v>
+        <f t="shared" si="74"/>
+        <v>5.5742802217257479</v>
       </c>
       <c r="BE24" s="1">
-        <f t="shared" si="67"/>
-        <v>5.9762901664826593</v>
-      </c>
-    </row>
-    <row r="25" spans="2:60" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="74"/>
+        <v>5.6809558023833002</v>
+      </c>
+    </row>
+    <row r="25" spans="2:75" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
         <v>1</v>
       </c>
@@ -4588,6 +4931,21 @@
       <c r="Z25" s="2">
         <v>104.79300000000001</v>
       </c>
+      <c r="AA25" s="2">
+        <v>121.916</v>
+      </c>
+      <c r="AB25" s="2">
+        <f>+AA25</f>
+        <v>121.916</v>
+      </c>
+      <c r="AC25" s="2">
+        <f>+AB25</f>
+        <v>121.916</v>
+      </c>
+      <c r="AD25" s="2">
+        <f>+AC25</f>
+        <v>121.916</v>
+      </c>
       <c r="AS25" s="2">
         <f>R25</f>
         <v>105.59399999999999</v>
@@ -4601,64 +4959,64 @@
         <v>108.474</v>
       </c>
       <c r="AV25" s="2">
-        <f t="shared" ref="AV25:BE25" si="68">+AU25</f>
+        <f t="shared" ref="AV25:BE25" si="75">+AU25</f>
         <v>108.474</v>
       </c>
       <c r="AW25" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>108.474</v>
       </c>
       <c r="AX25" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>108.474</v>
       </c>
       <c r="AY25" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>108.474</v>
       </c>
       <c r="AZ25" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>108.474</v>
       </c>
       <c r="BA25" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>108.474</v>
       </c>
       <c r="BB25" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>108.474</v>
       </c>
       <c r="BC25" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>108.474</v>
       </c>
       <c r="BD25" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>108.474</v>
       </c>
       <c r="BE25" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>108.474</v>
       </c>
     </row>
-    <row r="26" spans="2:60" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:75" x14ac:dyDescent="0.25">
       <c r="BG26" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="BH26" s="22">
         <v>0.09</v>
       </c>
     </row>
-    <row r="27" spans="2:60" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:75" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="V27" s="22">
-        <f t="shared" ref="V27:W27" si="69">+V13/R13-1</f>
+        <f t="shared" ref="V27:W27" si="76">+V13/R13-1</f>
         <v>0.65949226399449579</v>
       </c>
       <c r="W27" s="22">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>0.80265512837877062</v>
       </c>
       <c r="X27" s="22">
@@ -4675,35 +5033,49 @@
       </c>
       <c r="AA27" s="22">
         <f>+AA13/W13-1</f>
-        <v>-0.50223591334343176</v>
-      </c>
-      <c r="AB27" s="22"/>
-      <c r="AC27" s="22"/>
-      <c r="AD27" s="22"/>
-      <c r="BH27" s="22"/>
-    </row>
-    <row r="28" spans="2:60" x14ac:dyDescent="0.25">
+        <v>-0.41249347607042752</v>
+      </c>
+      <c r="AB27" s="22">
+        <f t="shared" ref="AB27:AD27" si="77">+AB13/X13-1</f>
+        <v>-0.40172576588429543</v>
+      </c>
+      <c r="AC27" s="22">
+        <f t="shared" si="77"/>
+        <v>-7.1905998552513894E-2</v>
+      </c>
+      <c r="AD27" s="22">
+        <f t="shared" si="77"/>
+        <v>-0.15200473215676624</v>
+      </c>
+      <c r="BG27" t="s">
+        <v>259</v>
+      </c>
+      <c r="BH27" s="22">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="28" spans="2:75" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
         <v>173</v>
       </c>
       <c r="R28" s="22">
-        <f t="shared" ref="R28:V28" si="70">+R15/R13</f>
+        <f t="shared" ref="R28:V28" si="78">+R15/R13</f>
         <v>0.88866402373097508</v>
       </c>
       <c r="S28" s="22">
-        <f t="shared" si="70"/>
+        <f t="shared" si="78"/>
         <v>0.87771849544337588</v>
       </c>
       <c r="T28" s="22">
-        <f t="shared" si="70"/>
+        <f t="shared" si="78"/>
         <v>0.87726317123640574</v>
       </c>
       <c r="U28" s="22">
-        <f t="shared" si="70"/>
+        <f t="shared" si="78"/>
         <v>0.80374399883561887</v>
       </c>
       <c r="V28" s="22">
-        <f t="shared" si="70"/>
+        <f t="shared" si="78"/>
         <v>0.79906903281165764</v>
       </c>
       <c r="W28" s="22">
@@ -4724,13 +5096,22 @@
       </c>
       <c r="AA28" s="22">
         <f>+AA15/AA13</f>
-        <v>0</v>
-      </c>
-      <c r="AB28" s="22"/>
-      <c r="AC28" s="22"/>
-      <c r="AD28" s="22"/>
+        <v>0.75160771704180063</v>
+      </c>
+      <c r="AB28" s="22">
+        <f t="shared" ref="AB28:AD28" si="79">+AB15/AB13</f>
+        <v>0.75000000000000011</v>
+      </c>
+      <c r="AC28" s="22">
+        <f t="shared" si="79"/>
+        <v>0.75000000000000011</v>
+      </c>
+      <c r="AD28" s="22">
+        <f t="shared" si="79"/>
+        <v>0.75000000000000011</v>
+      </c>
       <c r="AS28" s="22">
-        <f t="shared" ref="AS28" si="71">+AS15/AS13</f>
+        <f t="shared" ref="AS28" si="80">+AS15/AS13</f>
         <v>0.86868184851459884</v>
       </c>
       <c r="AT28" s="22">
@@ -4738,14 +5119,14 @@
         <v>0.821536191746009</v>
       </c>
       <c r="BG28" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="BH28" s="2">
-        <f>NPV(BH26,AV23:BE23)+Main!L5-Main!L6</f>
-        <v>3784.5611295339868</v>
-      </c>
-    </row>
-    <row r="29" spans="2:60" x14ac:dyDescent="0.25">
+        <f>NPV(BH26,AW23:BZ23)+Main!L5-Main!L6+AV23</f>
+        <v>3977.0952865305289</v>
+      </c>
+    </row>
+    <row r="29" spans="2:75" x14ac:dyDescent="0.25">
       <c r="AT29" s="22">
         <f>+AT13/AS13-1</f>
         <v>0.56176913482333446</v>
@@ -4754,12 +5135,15 @@
         <f>+AU13/AT13-1</f>
         <v>4.2891290536187343E-2</v>
       </c>
+      <c r="BG29" t="s">
+        <v>258</v>
+      </c>
       <c r="BH29" s="1">
         <f>+BH28/Main!L3</f>
-        <v>36.055725746678121</v>
-      </c>
-    </row>
-    <row r="31" spans="2:60" x14ac:dyDescent="0.25">
+        <v>37.670369437263332</v>
+      </c>
+    </row>
+    <row r="31" spans="2:75" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
         <v>157</v>
       </c>
@@ -4780,7 +5164,7 @@
         <v>111.72400000000005</v>
       </c>
     </row>
-    <row r="32" spans="2:60" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:75" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
         <v>3</v>
       </c>
@@ -5083,7 +5467,7 @@
     </row>
     <row r="54" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="W54" s="2">
         <f>+W23</f>
@@ -5104,7 +5488,7 @@
     </row>
     <row r="55" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="W55" s="2">
         <v>-447.50799999999998</v>
@@ -5116,7 +5500,7 @@
     </row>
     <row r="56" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="W56" s="2">
         <v>90.727999999999994</v>
@@ -5128,7 +5512,7 @@
     </row>
     <row r="57" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="W57" s="2">
         <v>41.427999999999997</v>
@@ -5140,7 +5524,7 @@
     </row>
     <row r="58" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="W58" s="2">
         <v>9.9779999999999998</v>
@@ -5164,7 +5548,7 @@
     </row>
     <row r="60" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="W60" s="2">
         <v>-1.9119999999999999</v>
@@ -5176,7 +5560,7 @@
     </row>
     <row r="61" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="W61" s="2">
         <v>1.6919999999999999</v>
@@ -5188,7 +5572,7 @@
     </row>
     <row r="62" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="W62" s="2">
         <f>-57.383+71.136-177.359-15.067-85.397-17.707</f>
@@ -5201,7 +5585,7 @@
     </row>
     <row r="63" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="W63" s="2">
         <f>SUM(W55:W62)</f>
@@ -5222,7 +5606,7 @@
     </row>
     <row r="65" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B65" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
@@ -5249,7 +5633,7 @@
     </row>
     <row r="66" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>
@@ -5277,7 +5661,7 @@
     </row>
     <row r="67" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B67" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
@@ -5304,7 +5688,7 @@
     </row>
     <row r="68" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B68" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
@@ -5331,7 +5715,7 @@
     </row>
     <row r="69" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B69" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C69" s="5"/>
       <c r="D69" s="5"/>
@@ -5359,7 +5743,7 @@
     </row>
     <row r="71" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B71" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
@@ -5386,7 +5770,7 @@
     </row>
     <row r="72" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B72" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C72" s="5"/>
       <c r="D72" s="5"/>
@@ -5413,7 +5797,7 @@
     </row>
     <row r="73" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B73" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
@@ -5440,7 +5824,7 @@
     </row>
     <row r="74" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B74" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C74" s="5"/>
       <c r="D74" s="5"/>
@@ -5468,7 +5852,7 @@
     </row>
     <row r="75" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B75" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
@@ -6031,7 +6415,7 @@
         <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -6290,7 +6674,7 @@
     </row>
     <row r="29" spans="3:7" ht="13" x14ac:dyDescent="0.3">
       <c r="C29" s="19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
